--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.87402806663832</v>
+        <v>2.254529560828727</v>
       </c>
       <c r="D2" t="n">
-        <v>14.74139968513911</v>
+        <v>2.395477448835106</v>
       </c>
       <c r="E2" t="n">
-        <v>12.26902021250808</v>
+        <v>1.993715784532563</v>
       </c>
       <c r="F2" t="n">
-        <v>13.54486822514223</v>
+        <v>2.201041086585612</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.88122118351877</v>
+        <v>4.530698442321801</v>
       </c>
       <c r="D3" t="n">
-        <v>17.19696796358761</v>
+        <v>2.794507294082987</v>
       </c>
       <c r="E3" t="n">
-        <v>12.26902021250808</v>
+        <v>1.993715784532563</v>
       </c>
       <c r="F3" t="n">
-        <v>13.54486822514223</v>
+        <v>2.201041086585612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.5993435540278</v>
+        <v>4.809893327529517</v>
       </c>
       <c r="D4" t="n">
-        <v>14.31782106327635</v>
+        <v>2.326645922782407</v>
       </c>
       <c r="E4" t="n">
-        <v>12.26902021250808</v>
+        <v>1.993715784532563</v>
       </c>
       <c r="F4" t="n">
-        <v>13.54486822514223</v>
+        <v>2.201041086585612</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.53467688275548</v>
+        <v>7.074384993447766</v>
       </c>
       <c r="D5" t="n">
-        <v>36.40054944640259</v>
+        <v>5.915089285040422</v>
       </c>
       <c r="E5" t="n">
-        <v>12.26902021250808</v>
+        <v>1.993715784532563</v>
       </c>
       <c r="F5" t="n">
-        <v>13.54486822514223</v>
+        <v>2.201041086585612</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.22376164123164</v>
+        <v>8.486361266700142</v>
       </c>
       <c r="D6" t="n">
-        <v>49.05382531238291</v>
+        <v>7.971246613262224</v>
       </c>
       <c r="E6" t="n">
-        <v>12.26902021250808</v>
+        <v>1.993715784532563</v>
       </c>
       <c r="F6" t="n">
-        <v>13.54486822514223</v>
+        <v>2.201041086585612</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.31723968202974</v>
+        <v>6.226551448329833</v>
       </c>
       <c r="D7" t="n">
-        <v>38.39165481567621</v>
+        <v>6.238643907547385</v>
       </c>
       <c r="E7" t="n">
-        <v>12.26902021250808</v>
+        <v>1.993715784532563</v>
       </c>
       <c r="F7" t="n">
-        <v>13.54486822514223</v>
+        <v>2.201041086585612</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
